--- a/Collections/USA/#USA#Regular#[1900-present]#circulation_quality.xlsx
+++ b/Collections/USA/#USA#Regular#[1900-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F005A5-5021-448F-8533-560B61A64A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308CA680-3178-4A0E-A55E-FC49CA3A6B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1¢" sheetId="1" r:id="rId1"/>
@@ -26984,7 +26984,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I124))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I124 I126 K126 K124">
+  <conditionalFormatting sqref="I126 I124 K126 K124">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27001,7 +27001,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(L124))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L124 L126">
+  <conditionalFormatting sqref="L126 L124">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27018,7 +27018,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I128))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I128 K128">
+  <conditionalFormatting sqref="K128 I128">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -27596,7 +27596,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I129))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I129 K129">
+  <conditionalFormatting sqref="K129 I129">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -40557,10 +40557,10 @@
         <v>3</v>
       </c>
       <c r="J130" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="32" t="s">
         <v>3</v>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="W130" s="11" t="str">
         <f t="shared" ref="W130:W139" si="7">IF((OR(AND(K130&gt;0,L130&gt;0),AND(K130&gt;0,L130="-"),AND(L130&gt;0,K130="-"))),"2",IF(OR(AND(K130=0,L130=0),AND(K130=0,L130="-"),AND(L130=0,K130="-"),AND(L130="-",K130="-")),"0","1"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">

--- a/Collections/USA/#USA#Regular#[1900-present]#circulation_quality.xlsx
+++ b/Collections/USA/#USA#Regular#[1900-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308CA680-3178-4A0E-A55E-FC49CA3A6B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F273D7E1-F191-4B42-A880-236DC6A729BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1¢" sheetId="1" r:id="rId1"/>
@@ -12317,7 +12317,7 @@
         <v>934</v>
       </c>
       <c r="H80" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I80" s="52">
         <v>2</v>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>3</v>
